--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Spells/moscow_spell.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Spells/moscow_spell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Spells\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33BEC29-DA46-441C-B8C4-6F61625EAECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A536DB2F-B02C-4CBC-8867-DD33D19A8D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="750" windowWidth="19395" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -88,6 +88,10 @@
   </si>
   <si>
     <t>Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectilePenetrationCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -512,6 +516,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
